--- a/results/Int Task Remove ACC 0.2/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_8_permute.xlsx
@@ -440,257 +440,257 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6639238084127441</v>
+        <v>0.6829222661996397</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6641436164612754</v>
+        <v>0.6825071917778985</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6660728055474145</v>
+        <v>0.6864961032087706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6642005246939049</v>
+        <v>0.7077417248316228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6654133814018205</v>
+        <v>0.7224098217918695</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6657793724729189</v>
+        <v>0.7096876307110969</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6684818021699109</v>
+        <v>0.7325199249949494</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6687016102184422</v>
+        <v>0.7061906198160157</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6685877937531832</v>
+        <v>0.7076801928050922</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6502185276132972</v>
+        <v>0.7170170553973191</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6410936481876151</v>
+        <v>0.7124266950828442</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6406540320905524</v>
+        <v>0.7119056290778305</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6348419231568134</v>
+        <v>0.7213563081353165</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.63412559077859</v>
+        <v>0.7152351163631087</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6443327936535939</v>
+        <v>0.7135257353255009</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6453180174309916</v>
+        <v>0.7230902308482456</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6460176330158802</v>
+        <v>0.7298630218840609</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6493304035078236</v>
+        <v>0.718304604160561</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6782749976525354</v>
+        <v>0.7190131116567978</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6803347199972685</v>
+        <v>0.6685227049621134</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6808312443269606</v>
+        <v>0.5682002486889766</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6857150377159311</v>
+        <v>0.5545742837387571</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6543614469487229</v>
+        <v>0.5354709013979507</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6835994741679305</v>
+        <v>0.5173762174805018</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6781778979806115</v>
+        <v>0.5147719544847955</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.677266299229178</v>
+        <v>0.5145276047609427</v>
       </c>
     </row>
     <row r="28">
@@ -700,583 +700,583 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6825192847773323</v>
+        <v>0.490149896284746</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6727026146487483</v>
+        <v>0.4883836070145087</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6727026146487483</v>
+        <v>0.4883836070145087</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6615592713469894</v>
+        <v>0.4870893003986422</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6669317641836656</v>
+        <v>0.4995760336669104</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.651873134476999</v>
+        <v>0.5005690823262947</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5995684221907962</v>
+        <v>0.5057217671144396</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5927063563650435</v>
+        <v>0.5059984833956004</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.52708476196709</v>
+        <v>0.5163362195291982</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5290463176105371</v>
+        <v>0.5278131873447472</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5339133942061729</v>
+        <v>0.5278131873447472</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5635519131125104</v>
+        <v>0.5191357488981143</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5812560642835396</v>
+        <v>0.5229126771624417</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5768687952242612</v>
+        <v>0.5157582452915551</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5814022473061066</v>
+        <v>0.5227095859072453</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5790177923589316</v>
+        <v>0.5194771982938912</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5788470676610432</v>
+        <v>0.5157404614688583</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5150966870872375</v>
+        <v>0.5161544688612378</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5161790105365592</v>
+        <v>0.5133303978170002</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5225936353832628</v>
+        <v>0.5145432545249159</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5021614458105582</v>
+        <v>0.5145432545249159</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5023567121837681</v>
+        <v>0.5084554963393779</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5039277350807955</v>
+        <v>0.5103032355175662</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5245374072040132</v>
+        <v>0.5076655389351901</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5118721243558699</v>
+        <v>0.5076655389351901</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5122871987776112</v>
+        <v>0.5083818713134135</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5122971577183213</v>
+        <v>0.5107183099393073</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4941210238929215</v>
+        <v>0.511931166647223</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4988764180820218</v>
+        <v>0.511931166647223</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4983798937523297</v>
+        <v>0.511931166647223</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4934715586880376</v>
+        <v>0.5230343185096872</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4906062291751436</v>
+        <v>0.516213511152591</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4906062291751436</v>
+        <v>0.5151390125852556</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4898084468889692</v>
+        <v>0.5256229317414204</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4978510028653295</v>
+        <v>0.52327866823354</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4983475271950217</v>
+        <v>0.5174430846538415</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4983475271950217</v>
+        <v>0.5174430846538415</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.497134670487106</v>
+        <v>0.5229048522804551</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4976311948167982</v>
+        <v>0.5170770935827431</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4957589139632885</v>
+        <v>0.5170770935827431</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4957589139632885</v>
+        <v>0.5187050247124</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4958972721038689</v>
+        <v>0.5179317841015471</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4989009597573433</v>
+        <v>0.5179317841015471</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4978510028653295</v>
+        <v>0.5187864746203509</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4989255014326647</v>
+        <v>0.5003336245137903</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4989255014326647</v>
+        <v>0.4992836676217765</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4996418338108882</v>
+        <v>0.4982091690544412</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5</v>
+        <v>0.4982091690544412</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5</v>
+        <v>0.4992836676217765</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5004965243296922</v>
+        <v>0.4997801919514687</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5</v>
+        <v>0.4997801919514687</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5004965243296922</v>
+        <v>0.5022628135999294</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5004965243296922</v>
+        <v>0.5022628135999294</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5004965243296922</v>
+        <v>0.5002767162811608</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5004965243296922</v>
+        <v>0.5002767162811608</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5004965243296922</v>
+        <v>0.4997801919514687</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5004965243296922</v>
+        <v>0.4997801919514687</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5004965243296922</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1286,41 +1286,41 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5006348824702725</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5002767162811608</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5014895729890765</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5014895729890765</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
